--- a/output/2026-10-07_02_Serbia_Grad_Beograd_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-07_02_Serbia_Grad_Beograd_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -494,10 +494,9 @@
           <t>+381 11 314 90 38</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato su iscar.com (pagina contatti Serbia); indirizzo Autoput 22, Zemun e telefono confermati.</t>
+          <t>Verificato su iscar.com (pagina contatti Serbia); indirizzo Autoput 22, Zemun e telefono confermati. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -512,7 +511,6 @@
           <t>S.V. Line d.o.o. (rappresentante TRUMPF)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Zemun, Grad Beograd</t>
@@ -528,7 +526,6 @@
           <t>011/307-3527</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Confermato come sede/rappresentante TRUMPF a Batajnički put 23 da trumpf.com (pagina ufficiale sito Belgrado). Telefono reperito via ricerca indipendente, assente nella lista originale.</t>
@@ -546,7 +543,6 @@
           <t>Teximp d.o.o. / HFO Teximp (Haas Factory Outlet)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -562,7 +558,6 @@
           <t>011/7129-428</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Confermato a Surčinski put 1B.</t>
@@ -580,7 +575,6 @@
           <t>Demax</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Savski Venac, Grad Beograd</t>
@@ -596,7 +590,6 @@
           <t>011/2650-999</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Confermato a Bulevar vojvode Mišića 39A.</t>
@@ -614,7 +607,6 @@
           <t>Fin import</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Savski Venac, Grad Beograd</t>
@@ -630,10 +622,9 @@
           <t>011/3657-204</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Confermato a Dobropoljska 33.</t>
+          <t>Confermato a Dobropoljska 33. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -648,7 +639,6 @@
           <t>A.P. Sidro</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Rakovica, Grad Beograd</t>
@@ -664,7 +654,6 @@
           <t>011/234-3358</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Confermato a Gočka 43B.</t>
@@ -682,7 +671,6 @@
           <t>Refit Inženjering</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -698,7 +686,6 @@
           <t>011/3573-673</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Confermato; risulta anche seconda sede a Rakovica (Patrijarha Dimitrija 24) stesso telefono.</t>
@@ -716,7 +703,6 @@
           <t>Elimp</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -732,7 +718,6 @@
           <t>011/2520-363</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Confermato a Mladena Mitrića 12.</t>
@@ -750,7 +735,6 @@
           <t>Honex</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Palilula, Grad Beograd</t>
@@ -766,7 +750,6 @@
           <t>011/2759-503</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Confermato a Mije Kovačevića 9.</t>
@@ -841,11 +824,9 @@
           <t>Utensili da taglio, utensili manuali, macchine per ingegneria meccanica</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>WebFetch fallito per errore DNS nell'ambiente; esistenza e attività confermate da fonte indipendente (RNIDS.rs, articolo sul 100.000esimo dominio .rs). Indirizzo e telefono non reperiti.</t>
+          <t>WebFetch fallito per errore DNS nell'ambiente; esistenza e attività confermate da fonte indipendente (RNIDS.rs, articolo sul 100.000esimo dominio .rs). Indirizzo e telefono non reperiti. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -860,7 +841,6 @@
           <t>SKF Grupa</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -876,7 +856,6 @@
           <t>011/311-6181</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Confermato a Bulevar Mihajla Pupina 10Z.</t>
@@ -894,7 +873,6 @@
           <t>Simex Trade</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Vračar, Grad Beograd</t>
@@ -910,7 +888,6 @@
           <t>011/344-2596</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Confermato a Mileševska 35; risulta anche sede a Čukarica.</t>
@@ -928,7 +905,6 @@
           <t>Avala Metal</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Savski Venac, Grad Beograd</t>
@@ -944,7 +920,6 @@
           <t>011/361-1310</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Confermato; fonte indica indirizzo Savska 33 II piano, leggermente diverso da quello fornito (Bulevar kralja Aleksandra 33), stesso telefono.</t>
@@ -962,7 +937,6 @@
           <t>Handler West</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -978,7 +952,6 @@
           <t>066/5744-628</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Confermato a Kosmajska 19B.</t>
@@ -996,7 +969,6 @@
           <t>Centum</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Palilula, Grad Beograd</t>
@@ -1012,10 +984,9 @@
           <t>011/2084-315</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Confermato a Višnjička 61B.</t>
+          <t>Confermato a Višnjička 61B. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1030,7 +1001,6 @@
           <t>Rolling World</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Stari Grad, Grad Beograd</t>
@@ -1046,7 +1016,6 @@
           <t>011/3242-155</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Confermato; azienda attiva da quasi 30 anni, uno dei maggiori distributori in Serbia.</t>
@@ -1064,7 +1033,6 @@
           <t>Ljubex International</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Voždovac, Grad Beograd</t>
@@ -1080,7 +1048,6 @@
           <t>011/3085-111</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Confermato a Bulevar Peka Dapčevića 253.</t>
@@ -1098,7 +1065,6 @@
           <t>N TRADE d.o.o.</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Grad Beograd (indirizzo esatto non reperito)</t>
@@ -1109,11 +1075,9 @@
           <t>Distributore autorizzato pneumatica/valvole industriali (ASCO, AVENTICS, TOPWORX, GEORGIN)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Confermato come distributore autorizzato di questi brand dal 1994; indirizzo esatto non reperito.</t>
+          <t>Confermato come distributore autorizzato di questi brand dal 1994; indirizzo esatto non reperito. [DUPLICATO — vedi anche: 2026-10-07_00_Serbia_Grad_Beograd_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1128,7 +1092,6 @@
           <t>Best Pneumatics</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Voždovac, Grad Beograd</t>
@@ -1144,7 +1107,6 @@
           <t>011/3221-758</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Confermato a Toplice Milana 14A.</t>
@@ -1162,7 +1124,6 @@
           <t>HIB tec</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Voždovac, Grad Beograd</t>
@@ -1178,7 +1139,6 @@
           <t>011/3085-200</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Confermato a Bulevar Peka Dapčevića 253.</t>
@@ -1196,7 +1156,6 @@
           <t>Industrijska oprema (Technological Solutions for Industrial Air)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Zemun, Grad Beograd</t>
@@ -1212,7 +1171,6 @@
           <t>011/3077-086</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Confermato a Banatska 28V.</t>
@@ -1230,7 +1188,6 @@
           <t>Ecotip Tedex</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Zemun, Grad Beograd</t>
@@ -1246,10 +1203,9 @@
           <t>011/2450-976</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Confermato a Taška Načića 5B; fonte terza cita sito ecotip-tedex.rs, non verificato direttamente.</t>
+          <t>Confermato a Taška Načića 5B; fonte terza cita sito ecotip-tedex.rs, non verificato direttamente. [DUPLICATO — vedi anche: 2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1264,7 +1220,6 @@
           <t>TRM Filter</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -1280,7 +1235,6 @@
           <t>011/313-3310</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Filiale locale di TRM Filter (Slovenia). Specializzazione principale del gruppo è il settore farmaceutico/chimico; rilevanza per Metalworking da verificare in fase di contatto commerciale.</t>
@@ -1298,7 +1252,6 @@
           <t>Korus</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>Zemun, Grad Beograd</t>
@@ -1314,7 +1267,6 @@
           <t>011/219-2731</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Esistenza confermata; dettaglio prodotti specifico non reperito oltre categoria generica.</t>
@@ -1332,7 +1284,6 @@
           <t>Pacomm</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Vračar, Grad Beograd</t>
@@ -1348,7 +1299,6 @@
           <t>011/308-7590</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Esistenza confermata; dettaglio prodotti specifico non reperito.</t>
@@ -1366,7 +1316,6 @@
           <t>Pavas oprema</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>Rakovica, Grad Beograd</t>
@@ -1382,7 +1331,6 @@
           <t>011/356-4861</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Esistenza confermata; dettaglio prodotti specifico non reperito.</t>
@@ -1400,7 +1348,6 @@
           <t>Pigo-R</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>Palilula, Grad Beograd</t>
@@ -1416,7 +1363,6 @@
           <t>011/275-5859</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Esistenza confermata a Uralska 9; dettaglio prodotti specifico non reperito.</t>
@@ -1434,7 +1380,6 @@
           <t>Prodock</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -1450,7 +1395,6 @@
           <t>011/236-1734</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Esistenza confermata su via Vodovodska; dettaglio prodotti specifico non reperito.</t>
@@ -1468,7 +1412,6 @@
           <t>Galeborough Company</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -1484,7 +1427,6 @@
           <t>011/311-5201</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Confermato a Bulevar Arsenija Čarnojevića 52A.</t>
@@ -1502,7 +1444,6 @@
           <t>Elit Impex</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Zemun, Grad Beograd</t>
@@ -1518,7 +1459,6 @@
           <t>011/316-3930</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Confermato a Gornjogradska 9.</t>
@@ -1536,7 +1476,6 @@
           <t>Colibri Ecco</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -1552,7 +1491,6 @@
           <t>011/215-8927</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Confermato; risultano due sedi sulla stessa via (Dr Ivana Ribara 191 e 205).</t>
@@ -1570,7 +1508,6 @@
           <t>Termovent Komerc</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -1586,7 +1523,6 @@
           <t>011/308-7966</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Confermato a Bulevar Milutina Milankovića 11A.</t>
@@ -1604,7 +1540,6 @@
           <t>Storage Systems</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -1620,7 +1555,6 @@
           <t>011/311-2442</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Confermato a Bulevar Mihajla Pupina 10D.</t>
@@ -1638,7 +1572,6 @@
           <t>BITO Lagertechnik</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>Rakovica, Grad Beograd</t>
@@ -1654,7 +1587,6 @@
           <t>011/2563-209</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Filiale locale di BITO-Lagertechnik Bittmann GmbH (gruppo tedesco globale).</t>
@@ -1672,7 +1604,6 @@
           <t>Hennlich</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>Voždovac, Grad Beograd</t>
@@ -1688,7 +1619,6 @@
           <t>011/630-9817</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>Filiale di Hennlich Group (azienda con oltre 100 anni di storia, presente in 22 paesi europei; filiale serba dal 2006).</t>
@@ -1706,7 +1636,6 @@
           <t>Dinako</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>Rakovica, Grad Beograd</t>
@@ -1722,7 +1651,6 @@
           <t>011/358-3374</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Confermato a Reljkovićeva 1.</t>
@@ -1740,7 +1668,6 @@
           <t>Eph Fero</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -1756,7 +1683,6 @@
           <t>011/2520-208</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>Confermato a Radnička 54.</t>
@@ -1774,7 +1700,6 @@
           <t>Elumatec</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -1790,10 +1715,9 @@
           <t>011/2394-832</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rappresentante locale di Elumatec (leader mondiale macchine per profili), confermato a Trgovačka 16.</t>
+          <t>Rappresentante locale di Elumatec (leader mondiale macchine per profili), confermato a Trgovačka 16. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1808,7 +1732,6 @@
           <t>Fero Tools</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -1824,10 +1747,9 @@
           <t>011/613-5832</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Confermato a Bulevar Mihajla Pupina 131.</t>
+          <t>Confermato a Bulevar Mihajla Pupina 131. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1842,7 +1764,6 @@
           <t>Feroks</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>Ripanj, Grad Beograd</t>
@@ -1853,8 +1774,6 @@
           <t>Vernici, utensili e elementi di fissaggio</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>Confermato a Put za Bošnjake 1; attività mista ferramenta/vernici, parzialmente coerente col settore (solo componente utensili/fissaggio).</t>
@@ -1872,7 +1791,6 @@
           <t>Feromerkur export</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -1888,10 +1806,9 @@
           <t>011/318-7330</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Confermato a Partizanske avijacije 25.</t>
+          <t>Confermato a Partizanske avijacije 25. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1906,7 +1823,6 @@
           <t>Entuziast</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -1922,10 +1838,9 @@
           <t>011/252-0098</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Confermato a Obalskih radnika 4A.</t>
+          <t>Confermato a Obalskih radnika 4A. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1940,7 +1855,6 @@
           <t>Interlignum-NS</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>Voždovac, Grad Beograd</t>
@@ -1956,10 +1870,9 @@
           <t>011/247-1768</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Confermato a Prilučka 1; ha anche sede a Novi Sad.</t>
+          <t>Confermato a Prilučka 1; ha anche sede a Novi Sad. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1974,7 +1887,6 @@
           <t>ITH Trading</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Stari Grad, Grad Beograd</t>
@@ -1990,7 +1902,6 @@
           <t>011/324-0627</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Confermato a Majke Jevrosime 26.</t>
@@ -2008,7 +1919,6 @@
           <t>Magrem</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -2024,7 +1934,6 @@
           <t>011/6151-500</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Confermato a Gandijeva 117A.</t>
@@ -2042,7 +1951,6 @@
           <t>Boltok</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>Zvezdara, Grad Beograd</t>
@@ -2053,8 +1961,6 @@
           <t>Elementi di fissaggio e utensili</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Confermato a Ruzveltova 38.</t>
@@ -2072,7 +1978,6 @@
           <t>Beotehnology</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -2088,10 +1993,9 @@
           <t>011/2589-569</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Confermato a Đorđa Stanojevića 9.</t>
+          <t>Confermato a Đorđa Stanojevića 9. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2106,7 +2010,6 @@
           <t>BTS company</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Savski Venac, Grad Beograd</t>
@@ -2122,10 +2025,9 @@
           <t>011/2656-068</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Confermato a Bulevar vojvode Mišića 14.</t>
+          <t>Confermato a Bulevar vojvode Mišića 14. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2140,7 +2042,6 @@
           <t>I.K.T. Commerce</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>Zvezdara, Grad Beograd</t>
@@ -2156,7 +2057,6 @@
           <t>011/347-7766</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>Confermato a Ustanička 189.</t>
@@ -2174,7 +2074,6 @@
           <t>Omega Air</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>Voždovac, Grad Beograd</t>
@@ -2190,7 +2089,6 @@
           <t>011/3477-609</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Rappresentante locale di Omega Air d.o.o. Ljubljana (Slovenia), produttore di compressori.</t>
@@ -2228,7 +2126,6 @@
           <t>011/414-5900</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Confermato via fonte EMIS (azienda registrata dal 2008, 11-50 dipendenti) a Auto-put za Novi Sad 110B.</t>
@@ -2246,7 +2143,6 @@
           <t>Extra Belt</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>Novi Beograd, Grad Beograd</t>
@@ -2262,7 +2158,6 @@
           <t>011/318-5743</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>Confermato a Vajara Živojina Lukića 58C.</t>
@@ -2280,7 +2175,6 @@
           <t>Balkanbelt plus</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>Čukarica, Grad Beograd</t>
@@ -2296,7 +2190,6 @@
           <t>011/2581-317</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Confermato a Lole Ribara 120.</t>
@@ -2314,7 +2207,6 @@
           <t>Hilti Store Beograd</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>Zemun, Grad Beograd</t>
@@ -2330,7 +2222,6 @@
           <t>011/6556-892</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>Entità Hilti SMN d.o.o. confermata (annunci di lavoro ufficiali); store Zemun elencato in directory settoriale, numero civico esatto non confermato indipendentemente.</t>
@@ -2348,7 +2239,6 @@
           <t>Iskra Servis</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>Palilula, Grad Beograd</t>
@@ -2364,10 +2254,9 @@
           <t>011/3290-295</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Confermato a Mije Kovačevića 10A.</t>
+          <t>Confermato a Mije Kovačevića 10A. [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">

--- a/output/2026-10-07_02_Serbia_Grad_Beograd_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-07_02_Serbia_Grad_Beograd_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
